--- a/results/final_N33_v5/Trend_Method_Comparison/Tables/Table_M6_Top_AC_Affected_Stations.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Tables/Table_M6_Top_AC_Affected_Stations.xlsx
@@ -469,8 +469,8 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
@@ -590,14 +590,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.032119481455827</v>
+        <v>1.677263</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>32.94192253017283</v>
+        <v>20.27</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.360)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
@@ -654,14 +654,14 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.033311336075184</v>
+        <v>1.706922</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>32.90392625434833</v>
+        <v>19.92</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.376)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
@@ -718,14 +718,14 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.098407255767618</v>
+        <v>1.656195</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>30.04350146698373</v>
+        <v>19.93</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>k=2(ρ=+0.405); k=6(ρ=+0.350)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -782,14 +782,14 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.029127931652926</v>
+        <v>2.725068</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>33.03768069475208</v>
+        <v>12.48</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.582); k=2(ρ=+0.361); k=9(ρ=−0.432); k=10(ρ=−0.351)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
@@ -846,14 +846,14 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.032126695881812</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>31.9728189685143</v>
+        <v>33</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>k=6(ρ=+0.384); k=10(ρ=−0.479)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -910,14 +910,14 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>1.328398</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>34</v>
+        <v>25.59</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.471); k=9(ρ=−0.494)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" s="3" t="n">
